--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_8.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_8.xlsx
@@ -471,156 +471,156 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57023</v>
+        <v>63315</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cauê Martins</t>
+          <t>Alexia da Luz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45080</v>
+        <v>45082</v>
       </c>
       <c r="G2" t="n">
-        <v>6553.9</v>
+        <v>3650.85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93613</v>
+        <v>6583</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Yago Teixeira</t>
+          <t>Nina Campos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45098</v>
+        <v>45081</v>
       </c>
       <c r="G3" t="n">
-        <v>8727.18</v>
+        <v>7636.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91369</v>
+        <v>87761</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr. Thales Santos</t>
+          <t>Emanuel Costela</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45106</v>
+        <v>45090</v>
       </c>
       <c r="G4" t="n">
-        <v>12076.9</v>
+        <v>8656.209999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3372</v>
+        <v>12371</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alexia Barbosa</t>
+          <t>Dr. Luiz Felipe da Mota</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45106</v>
+        <v>45081</v>
       </c>
       <c r="G5" t="n">
-        <v>7077.37</v>
+        <v>8448.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61907</v>
+        <v>35643</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ana Clara Novaes</t>
+          <t>João Miguel Cavalcanti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45080</v>
+        <v>45081</v>
       </c>
       <c r="G6" t="n">
-        <v>8394.370000000001</v>
+        <v>5866.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97199</v>
+        <v>18003</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lívia Cardoso</t>
+          <t>Srta. Sophie Rezende</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -630,133 +630,133 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45104</v>
+        <v>45105</v>
       </c>
       <c r="G7" t="n">
-        <v>4173.9</v>
+        <v>8822.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66232</v>
+        <v>97544</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nicolas Mendes</t>
+          <t>Ana Sophia Ferreira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45092</v>
+        <v>45089</v>
       </c>
       <c r="G8" t="n">
-        <v>4887</v>
+        <v>4519.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62515</v>
+        <v>97919</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ana Júlia Barbosa</t>
+          <t>Sr. Marcos Vinicius Gonçalves</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="G9" t="n">
-        <v>4257.83</v>
+        <v>3613.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20635</v>
+        <v>67318</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maria Vitória Cardoso</t>
+          <t>Ana Beatriz da Cruz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45097</v>
+        <v>45103</v>
       </c>
       <c r="G10" t="n">
-        <v>6467.66</v>
+        <v>4178.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>38187</v>
+        <v>37609</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natália Rocha</t>
+          <t>Levi Gomes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45105</v>
+        <v>45086</v>
       </c>
       <c r="G11" t="n">
-        <v>6395.75</v>
+        <v>9641.530000000001</v>
       </c>
     </row>
   </sheetData>
